--- a/output/pdf_financials_xlsx/MTT.xlsx
+++ b/output/pdf_financials_xlsx/MTT.xlsx
@@ -1305,13 +1305,13 @@
         <v>0.322772</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.06215</v>
+        <v>-1.06215</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.297406</v>
+        <v>-0.297406</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.740105</v>
+        <v>-1.740105</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.6014659999999999</v>
@@ -1355,13 +1355,13 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.046911</v>
+        <v>-0.500937</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.011889</v>
+        <v>-4.663605</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.645544</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1588,22 +1588,22 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.227013</v>
+        <v>-0.227013</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.325858</v>
+        <v>-2.325858</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.322772</v>
+        <v>-0.322772</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.06215</v>
+        <v>-1.06215</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.297406</v>
+        <v>-0.297406</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.740105</v>
+        <v>-1.740105</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.6014659999999999</v>
@@ -1765,22 +1765,22 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.227013</v>
+        <v>-0.227013</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.325858</v>
+        <v>-2.325858</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.322772</v>
+        <v>-0.322772</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.06215</v>
+        <v>-1.06215</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.297406</v>
+        <v>-0.297406</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.740105</v>
+        <v>-1.740105</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-0.6014659999999999</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>33.226543</v>
+        <v>-33.226543</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>35.405</v>
+        <v>-35.405</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>43.502625</v>
+        <v>-43.502625</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -2026,13 +2026,13 @@
         <v>0.322772</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.06215</v>
+        <v>-1.06215</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.297406</v>
+        <v>-0.297406</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.740105</v>
+        <v>-1.740105</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.6014659999999999</v>
@@ -2144,13 +2144,13 @@
         <v>0.322772</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.06215</v>
+        <v>-1.06215</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.297406</v>
+        <v>-0.297406</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.740105</v>
+        <v>-1.740105</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.6014659999999999</v>
@@ -2281,22 +2281,22 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>17.12555307311517</v>
+        <v>182.8744469268848</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.5085665814136432</v>
+        <v>199.4914334185864</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -42110,7 +42110,7 @@
         </is>
       </c>
       <c r="K359" s="5" t="n">
-        <v>1.740105</v>
+        <v>-1.740105</v>
       </c>
       <c r="L359" s="5" t="n">
         <v>-0.6014659999999999</v>
@@ -43156,10 +43156,10 @@
         </is>
       </c>
       <c r="I370" s="5" t="n">
-        <v>1.06215</v>
+        <v>-1.06215</v>
       </c>
       <c r="J370" s="5" t="n">
-        <v>0.297406</v>
+        <v>-0.297406</v>
       </c>
       <c r="K370" t="inlineStr">
         <is>
@@ -43921,10 +43921,10 @@
         </is>
       </c>
       <c r="H378" s="5" t="n">
-        <v>0.322772</v>
+        <v>-0.322772</v>
       </c>
       <c r="I378" s="5" t="n">
-        <v>1.06215</v>
+        <v>-1.06215</v>
       </c>
       <c r="J378" t="inlineStr">
         <is>
@@ -44886,10 +44886,10 @@
         </is>
       </c>
       <c r="G388" s="5" t="n">
-        <v>2.325858</v>
+        <v>-2.325858</v>
       </c>
       <c r="H388" s="5" t="n">
-        <v>0.322772</v>
+        <v>-0.322772</v>
       </c>
       <c r="I388" t="inlineStr">
         <is>
@@ -46135,10 +46135,10 @@
         </is>
       </c>
       <c r="F401" s="5" t="n">
-        <v>0.227013</v>
+        <v>-0.227013</v>
       </c>
       <c r="G401" s="5" t="n">
-        <v>2.325858</v>
+        <v>-2.325858</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MTT.xlsx
+++ b/output/pdf_financials_xlsx/MTT.xlsx
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001074</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>5.9e-05</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.273924</v>
+        <v>0.27285</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.337747</v>
+        <v>2.337688</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>0.322772</v>
@@ -2135,10 +2135,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.275583</v>
+        <v>0.274509</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.338499</v>
+        <v>2.33844</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>0.322772</v>
@@ -2429,52 +2429,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.313439</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.660063</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.246662</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.002423</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.085158</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000159</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.005307</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.140047</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000932</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>3.625681</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.094954</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.107898</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.07337200000000001</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.044215</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.994077</v>
       </c>
     </row>
     <row r="35">
@@ -2539,52 +2539,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.313439</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.660063</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.246662</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.002423</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.085158</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.042373</v>
+        <v>0.042532</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>2.23106</v>
+        <v>2.236367</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1.21455</v>
+        <v>1.354597</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.035</v>
+        <v>0.035932</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.186375</v>
+        <v>3.812056</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.124875</v>
+        <v>0.219829</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.0555</v>
+        <v>0.163398</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.016</v>
+        <v>0.08937199999999999</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.739437</v>
+        <v>0.783652</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-0.230091</v>
+        <v>1.763986</v>
       </c>
     </row>
     <row r="37">
@@ -3199,52 +3199,52 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.452813</v>
+        <v>0.139374</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.788687</v>
+        <v>0.128624</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.776289</v>
+        <v>1.529627</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.039888</v>
+        <v>0.037465</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.085158</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.000159</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.086547</v>
+        <v>0.08124000000000001</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.140047</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.000932</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.645841</v>
+        <v>0.02016</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.148215</v>
+        <v>0.053261</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.5441510000000001</v>
+        <v>0.436253</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.127253</v>
+        <v>0.053881</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.132117</v>
+        <v>0.08790199999999999</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>2.346409</v>
+        <v>0.352332</v>
       </c>
     </row>
     <row r="49">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
@@ -45258,7 +45258,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">

--- a/output/pdf_financials_xlsx/MTT.xlsx
+++ b/output/pdf_financials_xlsx/MTT.xlsx
@@ -7246,7 +7246,7 @@
         <v>0</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>0</v>
+        <v>0.390861</v>
       </c>
       <c r="L120" s="3" t="n">
         <v>0</v>
@@ -29680,7 +29680,11 @@
           <t>Issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MTT.xlsx
+++ b/output/pdf_financials_xlsx/MTT.xlsx
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.500937</v>
+        <v>-0.046911</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-4.663605</v>
+        <v>-0.011889</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0.645544</v>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>182.8744469268848</v>
+        <v>17.12555307311517</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>199.4914334185864</v>
+        <v>0.5085665814136432</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>200</v>
@@ -31506,7 +31506,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -35260,7 +35264,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -44778,7 +44786,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -46034,7 +46046,11 @@
           <t>Deferred income tax recovery (note 15)</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
